--- a/artfynd/A 33605-2023 artfynd.xlsx
+++ b/artfynd/A 33605-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 33605-2023 artfynd.xlsx
+++ b/artfynd/A 33605-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>85721568</v>
+        <v>99590130</v>
       </c>
       <c r="B2" t="n">
-        <v>103250</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,41 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221725</v>
+        <v>2809</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Brofallet, Vstm</t>
+          <t>Hällefors, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491391.3391718455</v>
+        <v>491377</v>
       </c>
       <c r="R2" t="n">
-        <v>6622907.755874618</v>
+        <v>6623024</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,27 +742,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1989-06-15</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1989-06-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Brofallet. Nära stig mot NO fr huset. Funnen tidigare i området (Binning 1921).</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,34 +756,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lars Asklund</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lars Asklund, Kjell Sundkvist</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>99590130</v>
+        <v>117386391</v>
       </c>
       <c r="B3" t="n">
-        <v>93044</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -831,21 +803,23 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hällefors, Vstm</t>
+          <t>Brofallet, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491377.4693959392</v>
+        <v>491343</v>
       </c>
       <c r="R3" t="n">
-        <v>6623023.72115478</v>
+        <v>6623052</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,22 +843,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-04-01</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-04-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,81 +857,70 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Jonas Göransson, Agnes Rengren, Albin Tengius, Amanda Evensen, Amanda Rudelius, Anton Björk, August Oljeqvist, Brian Johnson, Carl Teg, Carolina Neiker, Daniel Söderström, Edvin Johansson , Julia Lea Falk, Malin Henell, Malin Max Nordgren, Olavi Niemelä, Svea Nikula</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>99589197</v>
+        <v>117386360</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hällefors, Vstm</t>
+          <t>Brofallet, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491318.5792738872</v>
+        <v>491323</v>
       </c>
       <c r="R4" t="n">
-        <v>6623102.992791817</v>
+        <v>6623114</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -991,22 +944,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-04-01</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-04-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,82 +958,70 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Jonas Göransson, Agnes Rengren, Albin Tengius, Amanda Evensen, Amanda Rudelius, Anton Björk, August Oljeqvist, Brian Johnson, Carl Teg, Carolina Neiker, Daniel Söderström, Edvin Johansson , Julia Lea Falk, Malin Henell, Malin Max Nordgren, Olavi Niemelä, Svea Nikula</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>100445264</v>
+        <v>117386415</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hällefors, Vstm</t>
+          <t>Brofallet, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491314.722095704</v>
+        <v>491363</v>
       </c>
       <c r="R5" t="n">
-        <v>6623181.127016375</v>
+        <v>6622991</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1114,22 +1045,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-05-02</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>19:37</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-05-02</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>19:37</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,87 +1059,78 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Helena Backius</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Helena Backius</t>
+          <t>Jonas Göransson, Agnes Rengren, Albin Tengius, Amanda Evensen, Amanda Rudelius, Anton Björk, August Oljeqvist, Brian Johnson, Carl Teg, Carolina Neiker, Daniel Söderström, Edvin Johansson , Julia Lea Falk, Malin Henell, Malin Max Nordgren, Olavi Niemelä, Svea Nikula</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>100735033</v>
+        <v>101274982</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hällefors, Vstm</t>
+          <t>Gårdvikakällan, Hällefors, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491305.902737203</v>
+        <v>491364</v>
       </c>
       <c r="R6" t="n">
-        <v>6623079.836463281</v>
+        <v>6623113</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1242,22 +1154,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-05-12</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-05-12</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-30</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Hört alla läten under en månad</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1266,7 +1173,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1278,39 +1184,34 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Helena Backius</t>
+          <t>Helena Backius, Alexander Baker</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>101274982</v>
+        <v>110675780</v>
       </c>
       <c r="B7" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1318,31 +1219,36 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>pulli</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>pulli/nyligen flygga ungar</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gårdvikakällan, Hällefors, Vstm</t>
+          <t>Gårdvikabergets bäckskog , Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491363.5397762268</v>
+        <v>491420</v>
       </c>
       <c r="R7" t="n">
-        <v>6623113.473170497</v>
+        <v>6622934</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1366,27 +1272,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-05-30</t>
+          <t>2022-06-16</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-05-30</t>
+          <t>2022-06-16</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Hört alla läten under en månad</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1401,76 +1302,70 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Helena Backius</t>
+          <t>Thomas Pettersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Helena Backius, Alexander Baker</t>
+          <t>Alexander Baker, Helena Backius</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>102427752</v>
+        <v>109661812</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58286</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>103008</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hällefors, Vstm</t>
+          <t>Gårdvikabergets bäckskog , Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>491373.8732195874</v>
+        <v>491420</v>
       </c>
       <c r="R8" t="n">
-        <v>6622997.014743694</v>
+        <v>6622934</v>
       </c>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1494,22 +1389,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-07-23</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>19:32</t>
+          <t>2023-05-30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-07-23</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>19:32</t>
+          <t>2023-05-30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1536,64 +1421,69 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>102993133</v>
+        <v>100406451</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56816</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>205998</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>parning/parningsceremonier</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>ultraljudsdetektor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Brofallet källdråget, Vstm</t>
+          <t>Brofallet norra, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>491320.0681523623</v>
+        <v>491373</v>
       </c>
       <c r="R9" t="n">
-        <v>6623091.900449032</v>
+        <v>6622930</v>
       </c>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1617,22 +1507,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-08-20</t>
+          <t>2021-08-12</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>22:02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-08-20</t>
+          <t>2021-08-12</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>22:02</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Två individer. Liten ängsmark intill gammal skog.  Någon form av socialt läte? Parningsläte eller revirläte?</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1659,67 +1554,61 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>106002910</v>
+        <v>113505211</v>
       </c>
       <c r="B10" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56837</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>206002</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>parning/parningsceremonier</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>autobox</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Brofallet, Vstm</t>
+          <t>Brofallet källskogen, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491390.4387377371</v>
+        <v>491387</v>
       </c>
       <c r="R10" t="n">
-        <v>6622955.139794184</v>
+        <v>6622914</v>
       </c>
       <c r="S10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1743,22 +1632,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-01-15</t>
+          <t>2022-08-12</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>02:21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-01-15</t>
+          <t>2022-08-12</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>02:21</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1785,67 +1674,52 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>106002779</v>
+        <v>117386373</v>
       </c>
       <c r="B11" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Brofallet källskogen, Vstm</t>
+          <t>Brofallet, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491436.8264246648</v>
+        <v>491355</v>
       </c>
       <c r="R11" t="n">
-        <v>6622926.805555587</v>
+        <v>6623098</v>
       </c>
       <c r="S11" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1869,22 +1743,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-01-15</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-01-15</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1893,55 +1757,51 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Helena Backius</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Helena Backius</t>
+          <t>Jonas Göransson, Agnes Rengren, Albin Tengius, Amanda Evensen, Amanda Rudelius, Anton Björk, August Oljeqvist, Brian Johnson, Carl Teg, Carolina Neiker, Daniel Söderström, Edvin Johansson , Julia Lea Falk, Malin Henell, Malin Max Nordgren, Olavi Niemelä, Svea Nikula</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>109661812</v>
+        <v>99589197</v>
       </c>
       <c r="B12" t="n">
-        <v>56717</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103008</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1949,25 +1809,25 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gårdvikabergets bäckskog , Vstm</t>
+          <t>Hällefors, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491419.6764598669</v>
+        <v>491319</v>
       </c>
       <c r="R12" t="n">
-        <v>6622934.405918268</v>
+        <v>6623103</v>
       </c>
       <c r="S12" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1991,22 +1851,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-05-30</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-05-30</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2021,27 +1871,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Alexander Baker</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Alexander Baker</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>109780564</v>
+        <v>99601661</v>
       </c>
       <c r="B13" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2068,23 +1913,30 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Brofallet, Vstm</t>
+          <t>Brofallet norra, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>491398.8107175562</v>
+        <v>491373</v>
       </c>
       <c r="R13" t="n">
-        <v>6622863.380619331</v>
+        <v>6622930</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2108,22 +1960,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-06-04</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>13:41</t>
+          <t>2021-07-20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-06-04</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>13:41</t>
+          <t>2021-07-20</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2132,87 +1974,78 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Alexander Baker</t>
+          <t>Helena Backius</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Alexander Baker</t>
+          <t>Helena Backius</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>110675780</v>
+        <v>100445264</v>
       </c>
       <c r="B14" t="n">
-        <v>55611</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>pulli</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>pulli/nyligen flygga ungar</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gårdvikabergets bäckskog , Vstm</t>
+          <t>Hällefors, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491419.6764598669</v>
+        <v>491315</v>
       </c>
       <c r="R14" t="n">
-        <v>6622934.405918268</v>
+        <v>6623181</v>
       </c>
       <c r="S14" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2236,22 +2069,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-06-16</t>
+          <t>2022-05-02</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>19:37</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-06-16</t>
+          <t>2022-05-02</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>19:37</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2266,78 +2099,76 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Thomas Pettersson</t>
+          <t>Helena Backius</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Alexander Baker, Helena Backius</t>
+          <t>Helena Backius</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113505211</v>
+        <v>100735033</v>
       </c>
       <c r="B15" t="n">
-        <v>56185</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>206002</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>parning/parningsceremonier</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>autobox</t>
-        </is>
-      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Brofallet källskogen, Vstm</t>
+          <t>Hällefors, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>491387</v>
+        <v>491306</v>
       </c>
       <c r="R15" t="n">
-        <v>6622914</v>
+        <v>6623080</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2361,22 +2192,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2022-08-12</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>02:21</t>
+          <t>2022-05-12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2022-08-12</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>02:21</t>
+          <t>2022-05-12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2385,6 +2206,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2403,56 +2225,63 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117386415</v>
+        <v>101128216</v>
       </c>
       <c r="B16" t="n">
-        <v>90464</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Brofallet, Vstm</t>
+          <t>Hällefors, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>491363</v>
+        <v>491289</v>
       </c>
       <c r="R16" t="n">
-        <v>6622991</v>
+        <v>6623072</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2476,12 +2305,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2022-05-25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2022-05-25</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2490,75 +2319,77 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Helena Backius</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Jonas Göransson, Agnes Rengren, Albin Tengius, Amanda Evensen, Amanda Rudelius, Anton Björk, August Oljeqvist, Brian Johnson, Carl Teg, Carolina Neiker, Daniel Söderström, Edvin Johansson , Julia Lea Falk, Malin Henell, Malin Max Nordgren, Olavi Niemelä, Svea Nikula</t>
+          <t>Helena Backius</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117386411</v>
+        <v>102427752</v>
       </c>
       <c r="B17" t="n">
-        <v>90517</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Brofallet, Vstm</t>
+          <t>Hällefors, Vstm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491363</v>
+        <v>491374</v>
       </c>
       <c r="R17" t="n">
-        <v>6622991</v>
+        <v>6622997</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2582,12 +2413,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2022-07-23</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2022-07-23</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2596,76 +2437,77 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Alexander Baker</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jonas Göransson, Agnes Rengren, Albin Tengius, Amanda Evensen, Amanda Rudelius, Anton Björk, August Oljeqvist, Brian Johnson, Carl Teg, Carolina Neiker, Daniel Söderström, Edvin Johansson , Julia Lea Falk, Malin Henell, Malin Max Nordgren, Olavi Niemelä, Svea Nikula</t>
+          <t>Alexander Baker</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117386373</v>
+        <v>102993133</v>
       </c>
       <c r="B18" t="n">
-        <v>97753</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Brofallet, Vstm</t>
+          <t>Brofallet källdråget, Vstm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>491355</v>
+        <v>491320</v>
       </c>
       <c r="R18" t="n">
-        <v>6623098</v>
+        <v>6623092</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2689,12 +2531,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2022-08-20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2022-08-20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2703,75 +2545,80 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Helena Backius</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jonas Göransson, Agnes Rengren, Albin Tengius, Amanda Evensen, Amanda Rudelius, Anton Björk, August Oljeqvist, Brian Johnson, Carl Teg, Carolina Neiker, Daniel Söderström, Edvin Johansson , Julia Lea Falk, Malin Henell, Malin Max Nordgren, Olavi Niemelä, Svea Nikula</t>
+          <t>Helena Backius</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117386360</v>
+        <v>106002779</v>
       </c>
       <c r="B19" t="n">
-        <v>90464</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Brofallet, Vstm</t>
+          <t>Brofallet källskogen, Vstm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>491323</v>
+        <v>491387</v>
       </c>
       <c r="R19" t="n">
-        <v>6623114</v>
+        <v>6622914</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2795,12 +2642,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2023-01-15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2023-01-15</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2809,76 +2656,80 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Helena Backius</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jonas Göransson, Agnes Rengren, Albin Tengius, Amanda Evensen, Amanda Rudelius, Anton Björk, August Oljeqvist, Brian Johnson, Carl Teg, Carolina Neiker, Daniel Söderström, Edvin Johansson , Julia Lea Falk, Malin Henell, Malin Max Nordgren, Olavi Niemelä, Svea Nikula</t>
+          <t>Helena Backius</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117386441</v>
+        <v>106002910</v>
       </c>
       <c r="B20" t="n">
-        <v>96791</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Brofallet, Vstm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>491354</v>
+        <v>491390</v>
       </c>
       <c r="R20" t="n">
-        <v>6623085</v>
+        <v>6622955</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2902,12 +2753,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2023-01-15</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2023-01-15</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2922,66 +2773,62 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Helena Backius</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>August Oljeqvist, Agnes Rengren, Anton Björk, Jonas Göransson, Olavi Niemelä</t>
+          <t>Helena Backius</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117386391</v>
+        <v>109780564</v>
       </c>
       <c r="B21" t="n">
-        <v>94240</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2809</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Brofallet, Vstm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>491343</v>
+        <v>491398</v>
       </c>
       <c r="R21" t="n">
-        <v>6623052</v>
+        <v>6622863</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3008,12 +2855,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2023-06-04</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2023-06-04</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3022,22 +2879,229 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Alexander Baker</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Jonas Göransson, Agnes Rengren, Albin Tengius, Amanda Evensen, Amanda Rudelius, Anton Björk, August Oljeqvist, Brian Johnson, Carl Teg, Carolina Neiker, Daniel Söderström, Edvin Johansson , Julia Lea Falk, Malin Henell, Malin Max Nordgren, Olavi Niemelä, Svea Nikula</t>
+          <t>Alexander Baker</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>85721568</v>
+      </c>
+      <c r="B22" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Brofallet, Vstm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>491391</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6622908</v>
+      </c>
+      <c r="S22" t="n">
+        <v>50</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Hjulsjö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>1989-06-15</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>1989-06-15</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Brofallet. Nära stig mot NO fr huset. Funnen tidigare i området (Binning 1921).</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Lars Asklund</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Lars Asklund, Kjell Sundkvist</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>117386441</v>
+      </c>
+      <c r="B23" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Brofallet, Vstm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>491354</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6623085</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Hjulsjö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-05-29</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-05-29</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Olavi Niemelä, Jonas Göransson, Anton Björk, Agnes Rengren, August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33605-2023 artfynd.xlsx
+++ b/artfynd/A 33605-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -771,6 +776,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99590130</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -873,6 +883,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117386391</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -974,6 +989,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117386360</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1075,6 +1095,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117386415</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1188,6 +1213,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101274982</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1311,6 +1341,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110675780</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1418,6 +1453,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109661812</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1551,6 +1591,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100406451</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1671,6 +1716,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113505211</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1773,6 +1823,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117386373</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1880,6 +1935,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99589197</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1990,6 +2050,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99601661</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2108,6 +2173,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100445264</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2222,6 +2292,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100735033</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2334,6 +2409,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101128216</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2452,6 +2532,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102427752</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2560,6 +2645,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102993133</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2671,6 +2761,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106002779</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2782,6 +2877,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106002910</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2894,6 +2994,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109780564</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3001,6 +3106,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85721568</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3102,8 +3212,37 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117386441</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>